--- a/data-source/驮篮数据.xlsx
+++ b/data-source/驮篮数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D958F8-C550-4ADB-A028-44034DCC8FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C1392E-BE60-4822-B925-91A68C9258D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -438,6 +438,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF02A5E3"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -776,7 +781,7 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="4">

--- a/data-source/驮篮数据.xlsx
+++ b/data-source/驮篮数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C1392E-BE60-4822-B925-91A68C9258D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8783EF21-9DEE-471A-A468-9512DB553096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="81">
   <si>
     <t>皮驮篮</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>驮篮数据</t>
+  </si>
+  <si>
+    <t>大师弓箭驮篮</t>
   </si>
 </sst>
 </file>
@@ -717,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20.265625" customWidth="1"/>
@@ -1194,69 +1197,69 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="8" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="B31" s="4">
         <v>20</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="15"/>
-      <c r="E31" s="4"/>
+      <c r="E31" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="F31" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B32" s="4">
         <v>20</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="15"/>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="4"/>
+      <c r="F32" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="4">
+        <v>20</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="11" t="s">
+      <c r="F33" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="B33" s="12">
-        <v>20</v>
-      </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="13" t="s">
-        <v>54</v>
       </c>
       <c r="B34" s="12">
         <v>20</v>
       </c>
       <c r="C34" s="12"/>
       <c r="D34" s="15"/>
-      <c r="E34" s="14" t="s">
-        <v>59</v>
+      <c r="E34" s="12" t="s">
+        <v>58</v>
       </c>
       <c r="F34" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="32.65" customHeight="1">
+    <row r="35" spans="1:6">
       <c r="A35" s="13" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B35" s="12">
         <v>20</v>
@@ -1264,9 +1267,25 @@
       <c r="C35" s="12"/>
       <c r="D35" s="15"/>
       <c r="E35" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="32.65" customHeight="1">
+      <c r="A36" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" s="12">
+        <v>20</v>
+      </c>
+      <c r="C36" s="12"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="F35" s="12" t="s">
+      <c r="F36" s="12" t="s">
         <v>11</v>
       </c>
     </row>

--- a/data-source/驮篮数据.xlsx
+++ b/data-source/驮篮数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8783EF21-9DEE-471A-A468-9512DB553096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A18A64-3E47-483F-A15E-ED8A9D70B364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="83">
   <si>
     <t>皮驮篮</t>
   </si>
@@ -268,6 +268,12 @@
   </si>
   <si>
     <t>大师弓箭驮篮</t>
+  </si>
+  <si>
+    <t>15+1</t>
+  </si>
+  <si>
+    <t>20+1</t>
   </si>
 </sst>
 </file>
@@ -871,12 +877,14 @@
       <c r="A10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="4">
-        <v>15</v>
+      <c r="B10" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="15"/>
-      <c r="E10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="F10" s="4" t="s">
         <v>13</v>
       </c>
@@ -885,8 +893,8 @@
       <c r="A11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="4">
-        <v>15</v>
+      <c r="B11" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4" t="s">
@@ -1003,8 +1011,8 @@
       <c r="A19" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="4">
-        <v>15</v>
+      <c r="B19" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="15"/>
@@ -1169,8 +1177,8 @@
       <c r="A29" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B29" s="4">
-        <v>20</v>
+      <c r="B29" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="15"/>
@@ -1199,8 +1207,8 @@
       <c r="A31" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B31" s="4">
-        <v>20</v>
+      <c r="B31" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="15"/>
@@ -1229,8 +1237,8 @@
       <c r="A33" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B33" s="4">
-        <v>20</v>
+      <c r="B33" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="15"/>
@@ -1245,8 +1253,8 @@
       <c r="A34" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B34" s="12">
-        <v>20</v>
+      <c r="B34" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="C34" s="12"/>
       <c r="D34" s="15"/>
@@ -1261,8 +1269,8 @@
       <c r="A35" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B35" s="12">
-        <v>20</v>
+      <c r="B35" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="C35" s="12"/>
       <c r="D35" s="15"/>
@@ -1277,8 +1285,8 @@
       <c r="A36" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B36" s="12">
-        <v>20</v>
+      <c r="B36" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="C36" s="12"/>
       <c r="D36" s="15"/>

--- a/data-source/驮篮数据.xlsx
+++ b/data-source/驮篮数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A18A64-3E47-483F-A15E-ED8A9D70B364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5800ACED-4CA9-4CC7-BCC8-F37951B13588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="85">
   <si>
     <t>皮驮篮</t>
   </si>
@@ -274,6 +274,12 @@
   </si>
   <si>
     <t>20+1</t>
+  </si>
+  <si>
+    <t>大宗师猎人的驮篮</t>
+  </si>
+  <si>
+    <t>击杀敌人时获得的红猎点增加10%</t>
   </si>
 </sst>
 </file>
@@ -726,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20.265625" customWidth="1"/>
@@ -1297,6 +1303,21 @@
         <v>11</v>
       </c>
     </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D37" s="15"/>
+      <c r="E37" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
